--- a/news_daily/2026-10-09.xlsx
+++ b/news_daily/2026-10-09.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BL32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1015,6 +1031,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1193,6 +1213,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1371,6 +1395,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1549,176 +1577,208 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Duke Energy</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T22:18:53+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Duke Energy utilities reach large-load payment settlement with North Carolina staff</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>'-0.157</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQOE1qbW5pVHNMU1BEaC0zbHNoTDNDYURveHphN3N1YW9KbDR5bzZOZy1yTGJtaTJOTVc1OXlmMXRKLWc4bUh0UzJ0Sm44cm5OcWNFWlI2VlNUNFc2MjAwVm5rMVpNOWZuVEJZdU9FWWV6MHhucUNINTJOcFc4amtqbmRHcE1FRkNOUXNoNmRRMjFGV2xyaXM1QkRiRjFKd1NRMFdqVnJ6ZEllanZfRnZXZlpzYzRqallZblNaVzE2SV9QZGVq?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Daily Energy Insider</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>6bda1835911d47859d52945442d2ddb3</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>06444bd58c8cbcd624721a08</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>58c1e6c2d04fd4210016b983</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>DUK-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>'-0.157</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQOE1qbW5pVHNMU1BEaC0zbHNoTDNDYURveHphN3N1YW9KbDR5bzZOZy1yTGJtaTJOTVc1OXlmMXRKLWc4bUh0UzJ0Sm44cm5OcWNFWlI2VlNUNFc2MjAwVm5rMVpNOWZuVEJZdU9FWWV6MHhucUNINTJOcFc4amtqbmRHcE1FRkNOUXNoNmRRMjFGV2xyaXM1QkRiRjFKd1NRMFdqVnJ6ZEllanZfRnZXZlpzYzRqallZblNaVzE2SV9QZGVq?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Daily Energy Insider</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>06444bd58c8cbcd624721a08</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>58c1e6c2d04fd4210016b983</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr">
-        <is>
-          <t>DUK-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>DUK</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr"/>
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1889,6 +1949,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2067,184 +2131,216 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T22:06:05+08:00</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Class action alleges consumers enrolled in Uber One subscription without consent</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>'-0.697</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPNlJNekZTa2luazNyMHBKXzdnYmJDdHc0LVRnWE5CaHNYcnpXRXB1ZUdPUGktN0xrT1plLVdfb1RJX3E2SzRkM1RLU0E2M0Vmc2pBSzRqcFFucFc0MHJDQTc4YW5mLV9nbU9PQjMyVTJBS2lCRG1nZ1ZaaWVDcEtBR0s2QTBTUFdRN2ZYMXRWOG5CUS1XNVZoYTBEd0M4UldLNXF3N19uS1FYM2NUYXNEcGJ3Q2lIZW9VQTlNWm04MkE5bTJQT1JyNWRTUFdLc1NFYU5RRHN3alMyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>6d96b90518d74cc7b54f8ec3dba86b9e</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>bdf57b2ff14a8f1cc48808c4</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>cf4be0c7b9098718f032aa3f</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>UBER-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>'-0.697</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPNlJNekZTa2luazNyMHBKXzdnYmJDdHc0LVRnWE5CaHNYcnpXRXB1ZUdPUGktN0xrT1plLVdfb1RJX3E2SzRkM1RLU0E2M0Vmc2pBSzRqcFFucFc0MHJDQTc4YW5mLV9nbU9PQjMyVTJBS2lCRG1nZ1ZaaWVDcEtBR0s2QTBTUFdRN2ZYMXRWOG5CUS1XNVZoYTBEd0M4UldLNXF3N19uS1FYM2NUYXNEcGJ3Q2lIZW9VQTlNWm04MkE5bTJQT1JyNWRTUFdLc1NFYU5RRHN3alMyUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>bdf57b2ff14a8f1cc48808c4</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>cf4be0c7b9098718f032aa3f</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr">
-        <is>
-          <t>UBER-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC9" s="4" t="inlineStr">
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="4" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="4" t="inlineStr">
+      <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2423,6 +2519,10 @@
       </c>
       <c r="BG10" s="3" t="inlineStr"/>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2473,13 +2573,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -2532,7 +2636,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>703321c575ed4987a8afbb0533320edb</t>
+        </is>
+      </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>779dab052980aaba39b31066</t>
@@ -2557,7 +2665,11 @@
       <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
       <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="inlineStr"/>
@@ -2593,6 +2705,18 @@
         </is>
       </c>
       <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2771,6 +2895,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2949,6 +3077,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3119,6 +3251,10 @@
       <c r="BF14" s="3" t="inlineStr"/>
       <c r="BG14" s="3" t="inlineStr"/>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3297,6 +3433,10 @@
       </c>
       <c r="BG15" s="3" t="inlineStr"/>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3347,13 +3487,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -3406,7 +3550,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>6971d1796b2f469da3f1a2b03c35d435</t>
+        </is>
+      </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>9b9875aaa852733b3ff4ea27</t>
@@ -3431,7 +3579,11 @@
       <c r="AL16" s="4" t="inlineStr"/>
       <c r="AM16" s="4" t="inlineStr"/>
       <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="4" t="inlineStr"/>
       <c r="AQ16" s="4" t="inlineStr"/>
       <c r="AR16" s="4" t="inlineStr"/>
@@ -3467,6 +3619,18 @@
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3637,6 +3801,10 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3815,6 +3983,10 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3993,6 +4165,10 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4163,6 +4339,10 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4341,6 +4521,10 @@
         </is>
       </c>
       <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr"/>
+      <c r="BL21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4391,13 +4575,17 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -4450,7 +4638,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>ce83585cd2a24cb6a6f71f0edf84f270</t>
+        </is>
+      </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
           <t>df60c898bd5a51b7ca55e7f0</t>
@@ -4475,7 +4667,11 @@
       <c r="AL22" s="4" t="inlineStr"/>
       <c r="AM22" s="4" t="inlineStr"/>
       <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="4" t="inlineStr"/>
       <c r="AQ22" s="4" t="inlineStr"/>
       <c r="AR22" s="4" t="inlineStr"/>
@@ -4519,6 +4715,18 @@
         </is>
       </c>
       <c r="BH22" s="4" t="inlineStr"/>
+      <c r="BI22" s="4" t="inlineStr"/>
+      <c r="BJ22" s="4" t="inlineStr"/>
+      <c r="BK22" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4697,6 +4905,10 @@
         </is>
       </c>
       <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BI23" s="3" t="inlineStr"/>
+      <c r="BJ23" s="3" t="inlineStr"/>
+      <c r="BK23" s="3" t="inlineStr"/>
+      <c r="BL23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4743,17 +4955,17 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -4806,7 +5018,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="inlineStr">
+        <is>
+          <t>771d5e73b83e44c9a35cfc84062deb2c</t>
+        </is>
+      </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
           <t>08957e2647ed4bc7fc7d5b67</t>
@@ -4833,7 +5049,7 @@
       <c r="AN24" s="4" t="inlineStr"/>
       <c r="AO24" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP24" s="4" t="inlineStr"/>
@@ -4867,6 +5083,18 @@
       <c r="BF24" s="4" t="inlineStr"/>
       <c r="BG24" s="4" t="inlineStr"/>
       <c r="BH24" s="4" t="inlineStr"/>
+      <c r="BI24" s="4" t="inlineStr"/>
+      <c r="BJ24" s="4" t="inlineStr"/>
+      <c r="BK24" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5045,6 +5273,10 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr"/>
+      <c r="BL25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5223,6 +5455,10 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr"/>
+      <c r="BL26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5393,184 +5629,216 @@
         </is>
       </c>
       <c r="BH27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr"/>
+      <c r="BL27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>NTAP</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>NetApp, Inc.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T03:48:28+08:00</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Can AWS Transform Make NetApp (NTAP) the Default Storage Landing Zone in the Cloud?</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.077</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOZEdVN2ZhN0FjOWhqbE1UM0xlYmdHbkl4bW5MOUkzRFZyc2RlU2dPMi0ybXdaQ19DdldfQTI3N3IyZ0k2d1c0bnFhb2ZlRERUNHR0R1g3b3hoRGFwRTFxd0NuV1lydEJHRWpOSFlkX19RN0N0R19vUVY3S2NOT1ZuZXg0d0Q3NnJyZFR0R0FQYkVna0JOZkFFUWtldTdGdHM?oc=5</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>7f9989433e784167aaacb23d86cb1acb</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7ed9fbcf54e0692fd1a99da5</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>ef9f73cb3ef5e6f868a0ffc6</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>NTAP-DEFAULT-001</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+      <c r="AK28" s="2" t="inlineStr"/>
+      <c r="AL28" s="2" t="inlineStr"/>
+      <c r="AM28" s="2" t="inlineStr"/>
+      <c r="AN28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>0.077</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOZEdVN2ZhN0FjOWhqbE1UM0xlYmdHbkl4bW5MOUkzRFZyc2RlU2dPMi0ybXdaQ19DdldfQTI3N3IyZ0k2d1c0bnFhb2ZlRERUNHR0R1g3b3hoRGFwRTFxd0NuV1lydEJHRWpOSFlkX19RN0N0R19vUVY3S2NOT1ZuZXg0d0Q3NnJyZFR0R0FQYkVna0JOZkFFUWtldTdGdHM?oc=5</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr"/>
-      <c r="X28" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z28" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA28" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="5" t="inlineStr"/>
-      <c r="AC28" s="5" t="inlineStr">
-        <is>
-          <t>7ed9fbcf54e0692fd1a99da5</t>
-        </is>
-      </c>
-      <c r="AD28" s="5" t="inlineStr">
-        <is>
-          <t>ef9f73cb3ef5e6f868a0ffc6</t>
-        </is>
-      </c>
-      <c r="AE28" s="5" t="inlineStr">
-        <is>
-          <t>NTAP-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF28" s="5" t="inlineStr"/>
-      <c r="AG28" s="5" t="inlineStr"/>
-      <c r="AH28" s="5" t="inlineStr"/>
-      <c r="AI28" s="5" t="inlineStr"/>
-      <c r="AJ28" s="5" t="inlineStr"/>
-      <c r="AK28" s="5" t="inlineStr"/>
-      <c r="AL28" s="5" t="inlineStr"/>
-      <c r="AM28" s="5" t="inlineStr"/>
-      <c r="AN28" s="5" t="inlineStr"/>
-      <c r="AO28" s="5" t="inlineStr"/>
-      <c r="AP28" s="5" t="inlineStr"/>
-      <c r="AQ28" s="5" t="inlineStr"/>
-      <c r="AR28" s="5" t="inlineStr"/>
-      <c r="AS28" s="5" t="inlineStr"/>
-      <c r="AT28" s="5" t="inlineStr"/>
-      <c r="AU28" s="5" t="inlineStr"/>
-      <c r="AV28" s="5" t="inlineStr"/>
-      <c r="AW28" s="5" t="inlineStr">
+      <c r="AP28" s="2" t="inlineStr"/>
+      <c r="AQ28" s="2" t="inlineStr"/>
+      <c r="AR28" s="2" t="inlineStr"/>
+      <c r="AS28" s="2" t="inlineStr"/>
+      <c r="AT28" s="2" t="inlineStr"/>
+      <c r="AU28" s="2" t="inlineStr"/>
+      <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX28" s="5" t="inlineStr"/>
-      <c r="AY28" s="5" t="inlineStr"/>
-      <c r="AZ28" s="5" t="inlineStr"/>
-      <c r="BA28" s="5" t="inlineStr"/>
-      <c r="BB28" s="5" t="inlineStr">
+      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AY28" s="2" t="inlineStr"/>
+      <c r="AZ28" s="2" t="inlineStr"/>
+      <c r="BA28" s="2" t="inlineStr"/>
+      <c r="BB28" s="2" t="inlineStr">
         <is>
           <t>NTAP</t>
         </is>
       </c>
-      <c r="BC28" s="5" t="inlineStr">
+      <c r="BC28" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD28" s="5" t="inlineStr"/>
-      <c r="BE28" s="5" t="inlineStr">
+      <c r="BD28" s="2" t="inlineStr"/>
+      <c r="BE28" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF28" s="5" t="inlineStr">
+      <c r="BF28" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG28" s="5" t="inlineStr">
+      <c r="BG28" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH28" s="5" t="inlineStr"/>
+      <c r="BH28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5741,6 +6009,10 @@
         </is>
       </c>
       <c r="BH29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr"/>
+      <c r="BL29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -5791,13 +6063,17 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -5850,7 +6126,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>914055f1ae794100999137c39b79a1bc</t>
+        </is>
+      </c>
       <c r="AC30" s="4" t="inlineStr">
         <is>
           <t>e72a515e26befc5ce8f1598e</t>
@@ -5875,7 +6155,11 @@
       <c r="AL30" s="4" t="inlineStr"/>
       <c r="AM30" s="4" t="inlineStr"/>
       <c r="AN30" s="4" t="inlineStr"/>
-      <c r="AO30" s="4" t="inlineStr"/>
+      <c r="AO30" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="4" t="inlineStr"/>
       <c r="AQ30" s="4" t="inlineStr"/>
       <c r="AR30" s="4" t="inlineStr"/>
@@ -5919,6 +6203,18 @@
         </is>
       </c>
       <c r="BH30" s="4" t="inlineStr"/>
+      <c r="BI30" s="4" t="inlineStr"/>
+      <c r="BJ30" s="4" t="inlineStr"/>
+      <c r="BK30" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6097,179 +6393,203 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr"/>
+      <c r="BL31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>ExxonMobil</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T00:35:05+08:00</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>埃克森美孚、殼牌、BP勝訴 成功駁回紐約市環保訴訟‌</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2701987</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>52d85bdcc9e947e28eb8956f080471b3</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>208f2000be01297ec71708c7</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>2b3099325cb0d6bbe8f1a160</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>XOM-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+      <c r="AK32" s="2" t="inlineStr"/>
+      <c r="AL32" s="2" t="inlineStr"/>
+      <c r="AM32" s="2" t="inlineStr"/>
+      <c r="AN32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr"/>
-      <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr">
+      <c r="AP32" s="2" t="inlineStr"/>
+      <c r="AQ32" s="2" t="inlineStr"/>
+      <c r="AR32" s="2" t="inlineStr"/>
+      <c r="AS32" s="2" t="inlineStr"/>
+      <c r="AT32" s="2" t="inlineStr"/>
+      <c r="AU32" s="2" t="inlineStr"/>
+      <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" s="2" t="inlineStr"/>
+      <c r="AX32" s="2" t="inlineStr"/>
+      <c r="AY32" s="2" t="inlineStr"/>
+      <c r="AZ32" s="2" t="inlineStr"/>
+      <c r="BA32" s="2" t="inlineStr"/>
+      <c r="BB32" s="2" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="BC32" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2701987</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z32" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA32" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>208f2000be01297ec71708c7</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="inlineStr">
-        <is>
-          <t>2b3099325cb0d6bbe8f1a160</t>
-        </is>
-      </c>
-      <c r="AE32" s="4" t="inlineStr">
-        <is>
-          <t>XOM-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF32" s="4" t="inlineStr"/>
-      <c r="AG32" s="4" t="inlineStr"/>
-      <c r="AH32" s="4" t="inlineStr"/>
-      <c r="AI32" s="4" t="inlineStr"/>
-      <c r="AJ32" s="4" t="inlineStr"/>
-      <c r="AK32" s="4" t="inlineStr"/>
-      <c r="AL32" s="4" t="inlineStr"/>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP32" s="4" t="inlineStr"/>
-      <c r="AQ32" s="4" t="inlineStr"/>
-      <c r="AR32" s="4" t="inlineStr"/>
-      <c r="AS32" s="4" t="inlineStr"/>
-      <c r="AT32" s="4" t="inlineStr"/>
-      <c r="AU32" s="4" t="inlineStr"/>
-      <c r="AV32" s="4" t="inlineStr"/>
-      <c r="AW32" s="4" t="inlineStr"/>
-      <c r="AX32" s="4" t="inlineStr"/>
-      <c r="AY32" s="4" t="inlineStr"/>
-      <c r="AZ32" s="4" t="inlineStr"/>
-      <c r="BA32" s="4" t="inlineStr"/>
-      <c r="BB32" s="4" t="inlineStr">
+      <c r="BD32" s="2" t="inlineStr">
         <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="BC32" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD32" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BE32" s="4" t="inlineStr"/>
-      <c r="BF32" s="4" t="inlineStr"/>
-      <c r="BG32" s="4" t="inlineStr"/>
-      <c r="BH32" s="4" t="inlineStr"/>
+      <c r="BE32" s="2" t="inlineStr"/>
+      <c r="BF32" s="2" t="inlineStr"/>
+      <c r="BG32" s="2" t="inlineStr"/>
+      <c r="BH32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH32"/>
+  <autoFilter ref="A1:BL32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6280,7 +6600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6343,6 +6663,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6644,6 +6968,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -6824,176 +7168,192 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>DUK</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Duke Energy</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T22:18:53+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Duke Energy utilities reach large-load payment settlement with North Carolina staff</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09T21:06:54+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>奈飛據報計劃裁員約5%</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>'-0.157</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQOE1qbW5pVHNMU1BEaC0zbHNoTDNDYURveHphN3N1YW9KbDR5bzZOZy1yTGJtaTJOTVc1OXlmMXRKLWc4bUh0UzJ0Sm44cm5OcWNFWlI2VlNUNFc2MjAwVm5rMVpNOWZuVEJZdU9FWWV6MHhucUNINTJOcFc4amtqbmRHcE1FRkNOUXNoNmRRMjFGV2xyaXM1QkRiRjFKd1NRMFdqVnJ6ZEllanZfRnZXZlpzYzRqallZblNaVzE2SV9QZGVq?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>Daily Energy Insider</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>06444bd58c8cbcd624721a08</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>58c1e6c2d04fd4210016b983</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>DUK-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>DUK</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr"/>
-      <c r="BG3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2703699</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>裁員</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>6cb80e58b933ec256b215690</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>a8be937b4df9356931725bf5</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>NFLX-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD3" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BE3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG3" s="3" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7008,22 +7368,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T22:06:05+08:00</t>
+          <t>2026-10-09T20:57:07+08:00</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Class action alleges consumers enrolled in Uber One subscription without consent</t>
+          <t>ExxonMobil blocked $5B Kashagan environmental fine settlement</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -7034,7 +7394,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -7044,13 +7404,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -7060,7 +7424,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>'-0.697</t>
+          <t>'-0.715</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -7074,12 +7438,12 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPNlJNekZTa2luazNyMHBKXzdnYmJDdHc0LVRnWE5CaHNYcnpXRXB1ZUdPUGktN0xrT1plLVdfb1RJX3E2SzRkM1RLU0E2M0Vmc2pBSzRqcFFucFc0MHJDQTc4YW5mLV9nbU9PQjMyVTJBS2lCRG1nZ1ZaaWVDcEtBR0s2QTBTUFdRN2ZYMXRWOG5CUS1XNVZoYTBEd0M4UldLNXF3N19uS1FYM2NUYXNEcGJ3Q2lIZW9VQTlNWm04MkE5bTJQT1JyNWRTUFdLc1NFYU5RRHN3alMyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNWmhWU09jeGNRc3BmZTVyMDhub1FzVDlONkVIb2FfN1B2ZXQyZVNoTWtsR2Vzd3U3c2gxSlNFT25lWWdIbGJEVFZvcEZjM18zemFDRlV6NmFWTk94SkVfcmw4SjRRYWZ6TVcwLXViM3pZQ1VFZ21KNG14czdXTHBCX2tvaDY3UQ?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Top Class Actions</t>
+          <t>Quartz</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr"/>
@@ -7090,12 +7454,12 @@
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr">
@@ -7103,20 +7467,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>703321c575ed4987a8afbb0533320edb</t>
+        </is>
+      </c>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>bdf57b2ff14a8f1cc48808c4</t>
+          <t>779dab052980aaba39b31066</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>cf4be0c7b9098718f032aa3f</t>
+          <t>c606353d3b2cff933a7469b2</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>UBER-MAJOR_LITIGATION-001</t>
+          <t>XOM-REGULATORY_PENALTY-001</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr"/>
@@ -7128,7 +7496,11 @@
       <c r="AL4" s="4" t="inlineStr"/>
       <c r="AM4" s="4" t="inlineStr"/>
       <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="4" t="inlineStr"/>
       <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="inlineStr"/>
@@ -7136,18 +7508,14 @@
       <c r="AT4" s="4" t="inlineStr"/>
       <c r="AU4" s="4" t="inlineStr"/>
       <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW4" s="4" t="inlineStr"/>
       <c r="AX4" s="4" t="inlineStr"/>
       <c r="AY4" s="4" t="inlineStr"/>
       <c r="AZ4" s="4" t="inlineStr"/>
       <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
@@ -7158,20 +7526,28 @@
       <c r="BD4" s="4" t="inlineStr"/>
       <c r="BE4" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr"/>
       <c r="BG4" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -7184,20 +7560,24 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Delta Air Lines, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09T21:06:54+08:00</t>
+          <t>2026-10-09T20:43:17+08:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>奈飛據報計劃裁員約5%</t>
+          <t>Delta Air Lines Shares Fall as Third-Quarter Earnings Miss Forecasts and Full-Year Outlook Is Cut</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -7208,7 +7588,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>財報不如預期</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -7221,11 +7601,7 @@
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr">
         <is>
           <t>False</t>
@@ -7238,7 +7614,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>'-0.964</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -7247,33 +7623,33 @@
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2703699</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQk8wUDB2ZXNsLWJRUXVraXJTQ01OME9SY2RrVHlXYWw3bFFtSjFRV0NUNXRXYkZSYjZMQ3d5VUt3T1E1UWVRaERmbWRING5kUWJ6OU1vQjRMVEhaZ0pvQXpncnZmRDBOdlZHOUhoYlNGWndqbExJWkI0ek9kTEsydkp4TFRST3BKYWFFMEY5cTRnRzVSbkFv?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>EARNINGS_MISS</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>裁員</t>
+          <t>earnings miss</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -7284,17 +7660,17 @@
       <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>6cb80e58b933ec256b215690</t>
+          <t>36d7ad0282838aa544c72d9d</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>a8be937b4df9356931725bf5</t>
+          <t>65abd5e282d9ab8570074472</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
+          <t>DAL-EARNINGS_MISS-001</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr"/>
@@ -7306,11 +7682,7 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AO5" s="3" t="inlineStr"/>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -7318,208 +7690,220 @@
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
       <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX5" s="3" t="inlineStr"/>
       <c r="AY5" s="3" t="inlineStr"/>
       <c r="AZ5" s="3" t="inlineStr"/>
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD5" s="3" t="inlineStr"/>
       <c r="BE5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr"/>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:57:07+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>ExxonMobil blocked $5B Kashagan environmental fine settlement</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Lumentum</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09T20:27:58+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>美股盤前要點｜馬斯克、黃仁勛獲頒國家科學獎，蘋果被曝砍單iPhone 18 Pro系列</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>重大客戶流失</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>'-0.715</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNWmhWU09jeGNRc3BmZTVyMDhub1FzVDlONkVIb2FfN1B2ZXQyZVNoTWtsR2Vzd3U3c2gxSlNFT25lWWdIbGJEVFZvcEZjM18zemFDRlV6NmFWTk94SkVfcmw4SjRRYWZ6TVcwLXViM3pZQ1VFZ21KNG14czdXTHBCX2tvaDY3UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Quartz</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/p/6916154</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_CUSTOMER_LOSS</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>砍單</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>779dab052980aaba39b31066</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>c606353d3b2cff933a7469b2</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>e57f1cfc4516e759461039be</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>3671c2ebe9ded299a83099f5</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>LITE-MAJOR_CUSTOMER_LOSS-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD6" s="3" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -7532,24 +7916,20 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Delta Air Lines, Inc. Common Stock</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09T20:43:17+08:00</t>
+          <t>2026-10-09T20:17:58+08:00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Delta Air Lines Shares Fall as Third-Quarter Earnings Miss Forecasts and Full-Year Outlook Is Cut</t>
+          <t>據《Puck News》報導，奈飛計劃裁員5%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -7560,7 +7940,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -7573,7 +7953,11 @@
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
           <t>False</t>
@@ -7586,7 +7970,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>'-0.964</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr"/>
@@ -7595,33 +7979,33 @@
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQk8wUDB2ZXNsLWJRUXVraXJTQ01OME9SY2RrVHlXYWw3bFFtSjFRV0NUNXRXYkZSYjZMQ3d5VUt3T1E1UWVRaERmbWRING5kUWJ6OU1vQjRMVEhaZ0pvQXpncnZmRDBOdlZHOUhoYlNGWndqbExJWkI0ek9kTEsydkp4TFRST3BKYWFFMEY5cTRnRzVSbkFv?oc=5</t>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-NFLX/news/</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr"/>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>earnings miss</t>
+          <t>裁員</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -7632,17 +8016,17 @@
       <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>36d7ad0282838aa544c72d9d</t>
+          <t>c4cced58b22c5942630f7694</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>65abd5e282d9ab8570074472</t>
+          <t>b78c11d1ec8e3b594182e31d</t>
         </is>
       </c>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>DAL-EARNINGS_MISS-001</t>
+          <t>NFLX-WORKFORCE_REDUCTION-001</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr"/>
@@ -7654,7 +8038,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -7662,212 +8050,236 @@
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
       <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW7" s="3" t="inlineStr"/>
       <c r="AX7" s="3" t="inlineStr"/>
       <c r="AY7" s="3" t="inlineStr"/>
       <c r="AZ7" s="3" t="inlineStr"/>
       <c r="BA7" s="3" t="inlineStr"/>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="BC7" s="3" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD7" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="3" t="inlineStr"/>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Lumentum</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:27:58+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>美股盤前要點｜馬斯克、黃仁勛獲頒國家科學獎，蘋果被曝砍單iPhone 18 Pro系列</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>重大客戶流失</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T19:00:52+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Market Chatter: ExxonMobil Blocks Settlement Over $5.2 Billion Kazakhstan Fine</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>'-0.94</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPR011SnBsQVFuS3E5NmdESGd1ZEs2SFJDdDBHRUdPY0Rxdm9iNXhSTXRnUWZPZXpjZjVYaWRLbnJMcjcyN2ZpNzZQQTZqZl9IZXp5Yl9GS0FoTDNZbjdneXNEVmN3VnRKYXNNMHcwR3NyMmpSWXhtcjVVWDVQSmpTb1lIVUNQb2lERG9jOHpWcnBrQ3g1V3MzSDFyNWRMQ2hDbWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>6971d1796b2f469da3f1a2b03c35d435</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>9b9875aaa852733b3ff4ea27</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>9fdae8b7f4a952806c55de98</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>XOM-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/p/6916154</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_CUSTOMER_LOSS</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>砍單</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>e57f1cfc4516e759461039be</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>3671c2ebe9ded299a83099f5</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>LITE-MAJOR_CUSTOMER_LOSS-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="BC8" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -7880,20 +8292,24 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09T20:17:58+08:00</t>
+          <t>2026-10-09T16:33:51+08:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>據《Puck News》報導，奈飛計劃裁員5%</t>
+          <t>Flydubai and Boeing: Targets of Everest Ransomware Campaign</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -7904,7 +8320,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>資安攻擊</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -7917,11 +8333,7 @@
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
           <t>False</t>
@@ -7934,7 +8346,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>'-0.016</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
@@ -7943,33 +8355,33 @@
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-NFLX/news/</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9IeWE5RWdISlZodEhwbG8yZTlvQnBLWGxKWVd5SHZWM0dnUE0tRFkyTlFRd3lCdmtBY09La2kzbVg1WkNjUmp0VFFIa2VsaGJkTmFFRDBpM24zVFI4b0diTTR4eXRXYW40V2ZyZFRXdjlsZGF4?oc=5</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Cyber Magazine</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>CYBER_ATTACK</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>裁員</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -7980,17 +8392,17 @@
       <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>c4cced58b22c5942630f7694</t>
+          <t>54976da73037e7e74d4da018</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>b78c11d1ec8e3b594182e31d</t>
+          <t>07b4a0c0b95defc58dd555c3</t>
         </is>
       </c>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
+          <t>BA-CYBER_ATTACK-001</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr"/>
@@ -8002,11 +8414,7 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AO9" s="3" t="inlineStr"/>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -8021,371 +8429,415 @@
       <c r="BA9" s="3" t="inlineStr"/>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="BC9" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD9" s="3" t="inlineStr"/>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="3" t="inlineStr"/>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF9" s="3" t="inlineStr"/>
+      <c r="BG9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T19:00:52+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Market Chatter: ExxonMobil Blocks Settlement Over $5.2 Billion Kazakhstan Fine</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>PepsiCo, Inc.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09T16:03:10+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>PEP Q3 Deep Dive: International Growth Offsets North American Beverage Weakness, Margin Pressures Persist</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.94</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>0.853</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPR011SnBsQVFuS3E5NmdESGd1ZEs2SFJDdDBHRUdPY0Rxdm9iNXhSTXRnUWZPZXpjZjVYaWRLbnJMcjcyN2ZpNzZQQTZqZl9IZXp5Yl9GS0FoTDNZbjdneXNEVmN3VnRKYXNNMHcwR3NyMmpSWXhtcjVVWDVQSmpTb1lIVUNQb2lERG9jOHpWcnBrQ3g1V3MzSDFyNWRMQ2hDbWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYnQ5Ykt5akdWZUw4UU1kNTBJdEZsbk1mcl9hTGxGZDlUeVFfRDlCRVgxWXpwLVBKUlhUY2pjM0FWcGg2UzRFaUFNQXRuQ0xMMDRGUG1iLVNLaGN5Vlh6a05WZndUSkc1ajJjaHl0SlJ6NHlRbTZSZmZwNmFYWUxfbVBRQ2VBcU9rZVhsdFVHc3NWcjFyUkZOUkJDTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>9b9875aaa852733b3ff4ea27</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>9fdae8b7f4a952806c55de98</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>a2047f7e5f8d52985250fd13</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>75fdb756567aabe6eaf2652d</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>PEP-OPERATING_DETERIORATION-001</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG10" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T16:33:51+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Flydubai and Boeing: Targets of Everest Ransomware Campaign</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>資安攻擊</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T15:31:30+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Corteva agrees to end pesticide loyalty programmes in proposed settlement with Federal Trade Commission</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>0.126</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNTUIxVF9TUl81LXpaVHhkbER0Q0FmUlR4UjVBd3NJbTZINTZiUHdFOUhmd082RDV2TW5ESS05a0FFd2pjbks4c05EQzNQaUlwZVRRUTNvWVJPb0JEV0lKaHprQ04zSFB1LXdGOVRFUTI2RWs2N3ZpcnZyczQ0UWdGcEtnSGRXZFlhZ2YtQXhvUktvU28yYnRQOTVnZFhZa1BTZTR3SUxacmRHbldTTG9NT3hkY2FTeVJnMExnTUFGUWFSVFVKdkZRZ0hrV3MtZUY4SVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Oils &amp; Fats International</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>ce83585cd2a24cb6a6f71f0edf84f270</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>df60c898bd5a51b7ca55e7f0</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>51d2fa07a12405a6d72f546a</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>CTVA-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.016</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9IeWE5RWdISlZodEhwbG8yZTlvQnBLWGxKWVd5SHZWM0dnUE0tRFkyTlFRd3lCdmtBY09La2kzbVg1WkNjUmp0VFFIa2VsaGJkTmFFRDBpM24zVFI4b0diTTR4eXRXYW40V2ZyZFRXdjlsZGF4?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Cyber Magazine</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>CYBER_ATTACK</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>ransomware</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>54976da73037e7e74d4da018</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>07b4a0c0b95defc58dd555c3</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr">
-        <is>
-          <t>BA-CYBER_ATTACK-001</t>
-        </is>
-      </c>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr"/>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -8400,22 +8852,22 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09T16:03:10+08:00</t>
+          <t>2026-10-09T14:15:46+08:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>PEP Q3 Deep Dive: International Growth Offsets North American Beverage Weakness, Margin Pressures Persist</t>
+          <t>Netflix Is Sharpening the Layoff Axe</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -8426,7 +8878,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>營運惡化</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -8452,7 +8904,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>'-0.918</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr"/>
@@ -8466,12 +8918,12 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYnQ5Ykt5akdWZUw4UU1kNTBJdEZsbk1mcl9hTGxGZDlUeVFfRDlCRVgxWXpwLVBKUlhUY2pjM0FWcGg2UzRFaUFNQXRuQ0xMMDRGUG1iLVNLaGN5Vlh6a05WZndUSkc1ajJjaHl0SlJ6NHlRbTZSZmZwNmFYWUxfbVBRQ2VBcU9rZVhsdFVHc3NWcjFyUkZOUkJDTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE90dm1nWTNuR1dCeVJkcXp1SVBvMlpMTVQwUmJ3US1UYTBwbjY1b1piazlVRE8yVWZsQ29xOW85Yk5nbXlJWVU5RFhjTDhyZDBjSndja1g5bUx6cXgtVVNsdzlsRnJTZw?oc=5</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Puck</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr"/>
@@ -8482,12 +8934,12 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>OPERATING_DETERIORATION</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>margin pressure</t>
+          <t>layoff</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -8498,17 +8950,17 @@
       <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>a2047f7e5f8d52985250fd13</t>
+          <t>3304f9e80330a967e3017e37</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>75fdb756567aabe6eaf2652d</t>
+          <t>d1e2fb9f6d8799eaf17d49d8</t>
         </is>
       </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>PEP-OPERATING_DETERIORATION-001</t>
+          <t>NFLX-WORKFORCE_REDUCTION-001</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr"/>
@@ -8539,7 +8991,7 @@
       <c r="BA12" s="3" t="inlineStr"/>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="BC12" s="3" t="inlineStr">
@@ -8564,6 +9016,10 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr"/>
+      <c r="BL12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -8576,24 +9032,20 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T15:31:30+08:00</t>
+          <t>2026-10-09T05:31:41+08:00</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Corteva agrees to end pesticide loyalty programmes in proposed settlement with Federal Trade Commission</t>
+          <t>美國運通因反洗錢計劃不完善被罰款3.5億美元</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -8614,13 +9066,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -8630,7 +9086,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -8639,17 +9095,17 @@
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNTUIxVF9TUl81LXpaVHhkbER0Q0FmUlR4UjVBd3NJbTZINTZiUHdFOUhmd082RDV2TW5ESS05a0FFd2pjbks4c05EQzNQaUlwZVRRUTNvWVJPb0JEV0lKaHprQ04zSFB1LXdGOVRFUTI2RWs2N3ZpcnZyczQ0UWdGcEtnSGRXZFlhZ2YtQXhvUktvU28yYnRQOTVnZFhZa1BTZTR3SUxacmRHbldTTG9NT3hkY2FTeVJnMExnTUFGUWFSVFVKdkZRZ0hrV3MtZUY4SVE?oc=5</t>
+          <t>https://tw.tradingview.com/symbols/NYSE-AXP/news/</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>Oils &amp; Fats International</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr"/>
@@ -8665,7 +9121,7 @@
       </c>
       <c r="Z13" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>罰款</t>
         </is>
       </c>
       <c r="AA13" s="4" t="inlineStr">
@@ -8673,20 +9129,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>771d5e73b83e44c9a35cfc84062deb2c</t>
+        </is>
+      </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>df60c898bd5a51b7ca55e7f0</t>
+          <t>08957e2647ed4bc7fc7d5b67</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>51d2fa07a12405a6d72f546a</t>
+          <t>ba7c5621b413520ed3012946</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
         <is>
-          <t>CTVA-REGULATORY_PENALTY-001</t>
+          <t>AXP-REGULATORY_PENALTY-001</t>
         </is>
       </c>
       <c r="AF13" s="4" t="inlineStr"/>
@@ -8698,7 +9158,11 @@
       <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr"/>
       <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
       <c r="AR13" s="4" t="inlineStr"/>
@@ -8706,919 +9170,247 @@
       <c r="AT13" s="4" t="inlineStr"/>
       <c r="AU13" s="4" t="inlineStr"/>
       <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW13" s="4" t="inlineStr"/>
       <c r="AX13" s="4" t="inlineStr"/>
       <c r="AY13" s="4" t="inlineStr"/>
       <c r="AZ13" s="4" t="inlineStr"/>
       <c r="BA13" s="4" t="inlineStr"/>
       <c r="BB13" s="4" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="BE13" s="4" t="inlineStr"/>
+      <c r="BF13" s="4" t="inlineStr"/>
+      <c r="BG13" s="4" t="inlineStr"/>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T14:15:46+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Netflix Is Sharpening the Layoff Axe</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>SYY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Sysco Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T01:06:24+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Sysco-Restaurant Depot Deal Still Awaits FTC Review Six Months After Announcement</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>'-0.035</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTDY2cGxiOTFDVUpSZVdKNUFYUWdDa3ZKTndkQ3JFaUxYd2ZMb2pUcnVJM2J3emxuTE1wMHNKdndvRlFDTEtKWXNpbGs3Yk9BWVVkdDJWLVk5dHBhbTBBWER6UFdkY3RHWnd6MmtOZUcyYUdnVDN4UGNXWnpPQnNOVVR4ZVNqX3lsdDJuZ2FPZkhXLXQ3dHNQekFDYWkyOTdETWNFX1VTSUd2ZWxfdmJWbXd6azAzX0drY2pOMVdvZlQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Distribution Strategy Group</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>914055f1ae794100999137c39b79a1bc</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>e72a515e26befc5ce8f1598e</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>08f126b0d1618ed5c5092d09</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>SYY-REGULATORY_INVESTIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="inlineStr"/>
+      <c r="AG14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
+      <c r="AL14" s="4" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>'-0.918</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE90dm1nWTNuR1dCeVJkcXp1SVBvMlpMTVQwUmJ3US1UYTBwbjY1b1piazlVRE8yVWZsQ29xOW85Yk5nbXlJWVU5RFhjTDhyZDBjSndja1g5bUx6cXgtVVNsdzlsRnJTZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>Puck</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>3304f9e80330a967e3017e37</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>d1e2fb9f6d8799eaf17d49d8</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr">
-        <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AS14" s="4" t="inlineStr"/>
+      <c r="AT14" s="4" t="inlineStr"/>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX14" s="4" t="inlineStr"/>
+      <c r="AY14" s="4" t="inlineStr"/>
+      <c r="AZ14" s="4" t="inlineStr"/>
+      <c r="BA14" s="4" t="inlineStr"/>
+      <c r="BB14" s="4" t="inlineStr">
+        <is>
+          <t>SYY</t>
+        </is>
+      </c>
+      <c r="BC14" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BD14" s="4" t="inlineStr"/>
+      <c r="BE14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG14" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T05:31:41+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>美國運通因反洗錢計劃不完善被罰款3.5億美元</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-AXP/news/</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>罰款</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>08957e2647ed4bc7fc7d5b67</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>ba7c5621b413520ed3012946</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t>AXP-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr"/>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BC15" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD15" s="4" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BE15" s="4" t="inlineStr"/>
-      <c r="BF15" s="4" t="inlineStr"/>
-      <c r="BG15" s="4" t="inlineStr"/>
-      <c r="BH15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>NetApp, Inc.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-09T03:48:28+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Can AWS Transform Make NetApp (NTAP) the Default Storage Landing Zone in the Cloud?</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>0.077</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr"/>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOZEdVN2ZhN0FjOWhqbE1UM0xlYmdHbkl4bW5MOUkzRFZyc2RlU2dPMi0ybXdaQ19DdldfQTI3N3IyZ0k2d1c0bnFhb2ZlRERUNHR0R1g3b3hoRGFwRTFxd0NuV1lydEJHRWpOSFlkX19RN0N0R19vUVY3S2NOT1ZuZXg0d0Q3NnJyZFR0R0FQYkVna0JOZkFFUWtldTdGdHM?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z16" s="5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA16" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="5" t="inlineStr"/>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>7ed9fbcf54e0692fd1a99da5</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>ef9f73cb3ef5e6f868a0ffc6</t>
-        </is>
-      </c>
-      <c r="AE16" s="5" t="inlineStr">
-        <is>
-          <t>NTAP-DEFAULT-001</t>
-        </is>
-      </c>
-      <c r="AF16" s="5" t="inlineStr"/>
-      <c r="AG16" s="5" t="inlineStr"/>
-      <c r="AH16" s="5" t="inlineStr"/>
-      <c r="AI16" s="5" t="inlineStr"/>
-      <c r="AJ16" s="5" t="inlineStr"/>
-      <c r="AK16" s="5" t="inlineStr"/>
-      <c r="AL16" s="5" t="inlineStr"/>
-      <c r="AM16" s="5" t="inlineStr"/>
-      <c r="AN16" s="5" t="inlineStr"/>
-      <c r="AO16" s="5" t="inlineStr"/>
-      <c r="AP16" s="5" t="inlineStr"/>
-      <c r="AQ16" s="5" t="inlineStr"/>
-      <c r="AR16" s="5" t="inlineStr"/>
-      <c r="AS16" s="5" t="inlineStr"/>
-      <c r="AT16" s="5" t="inlineStr"/>
-      <c r="AU16" s="5" t="inlineStr"/>
-      <c r="AV16" s="5" t="inlineStr"/>
-      <c r="AW16" s="5" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX16" s="5" t="inlineStr"/>
-      <c r="AY16" s="5" t="inlineStr"/>
-      <c r="AZ16" s="5" t="inlineStr"/>
-      <c r="BA16" s="5" t="inlineStr"/>
-      <c r="BB16" s="5" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="BC16" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD16" s="5" t="inlineStr"/>
-      <c r="BE16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="5" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>SYY</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Sysco Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:06:24+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Sysco-Restaurant Depot Deal Still Awaits FTC Review Six Months After Announcement</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>'-0.035</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTDY2cGxiOTFDVUpSZVdKNUFYUWdDa3ZKTndkQ3JFaUxYd2ZMb2pUcnVJM2J3emxuTE1wMHNKdndvRlFDTEtKWXNpbGs3Yk9BWVVkdDJWLVk5dHBhbTBBWER6UFdkY3RHWnd6MmtOZUcyYUdnVDN4UGNXWnpPQnNOVVR4ZVNqX3lsdDJuZ2FPZkhXLXQ3dHNQekFDYWkyOTdETWNFX1VTSUd2ZWxfdmJWbXd6azAzX0drY2pOMVdvZlQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>Distribution Strategy Group</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>e72a515e26befc5ce8f1598e</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>08f126b0d1618ed5c5092d09</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr">
-        <is>
-          <t>SYY-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF17" s="4" t="inlineStr"/>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="4" t="inlineStr"/>
-      <c r="AS17" s="4" t="inlineStr"/>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr"/>
-      <c r="AW17" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX17" s="4" t="inlineStr"/>
-      <c r="AY17" s="4" t="inlineStr"/>
-      <c r="AZ17" s="4" t="inlineStr"/>
-      <c r="BA17" s="4" t="inlineStr"/>
-      <c r="BB17" s="4" t="inlineStr">
-        <is>
-          <t>SYY</t>
-        </is>
-      </c>
-      <c r="BC17" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="4" t="inlineStr"/>
-      <c r="BE17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T00:35:05+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>埃克森美孚、殼牌、BP勝訴 成功駁回紐約市環保訴訟‌</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2701987</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>208f2000be01297ec71708c7</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>2b3099325cb0d6bbe8f1a160</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr">
-        <is>
-          <t>XOM-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr"/>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BE18" s="4" t="inlineStr"/>
-      <c r="BF18" s="4" t="inlineStr"/>
-      <c r="BG18" s="4" t="inlineStr"/>
-      <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH18"/>
+  <autoFilter ref="A1:BL14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9629,7 +9421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9692,6 +9484,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9993,6 +9789,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -10173,6 +9989,10 @@
       </c>
       <c r="BG2" s="3" t="inlineStr"/>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -10343,6 +10163,10 @@
       <c r="BF3" s="3" t="inlineStr"/>
       <c r="BG3" s="3" t="inlineStr"/>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -10521,349 +10345,13 @@
       </c>
       <c r="BG4" s="3" t="inlineStr"/>
       <c r="BH4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T05:31:41+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>美國運通因反洗錢計劃不完善被罰款3.5億美元</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-AXP/news/</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>罰款</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>08957e2647ed4bc7fc7d5b67</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>ba7c5621b413520ed3012946</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr">
-        <is>
-          <t>AXP-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="4" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BE5" s="4" t="inlineStr"/>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T00:35:05+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>埃克森美孚、殼牌、BP勝訴 成功駁回紐約市環保訴訟‌</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2701987</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>208f2000be01297ec71708c7</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>2b3099325cb0d6bbe8f1a160</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr">
-        <is>
-          <t>XOM-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BE6" s="4" t="inlineStr"/>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr"/>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH6"/>
+  <autoFilter ref="A1:BL4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10874,7 +10362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10937,6 +10425,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11240,9 +10732,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11253,7 +10765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11303,134 +10815,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -11440,46 +10952,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -11488,12 +11034,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -11503,90 +11049,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -11596,94 +11146,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -11691,89 +11241,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-09.xlsx
+++ b/news_daily/2026-10-09.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1085,13 +1085,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1144,7 +1148,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>e64c9d39827d46e887fe11552793cc84</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>2026338b805069c2e1313420</t>
@@ -1169,7 +1177,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1215,8 +1227,16 @@
       <c r="BH3" s="3" t="inlineStr"/>
       <c r="BI3" s="3" t="inlineStr"/>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2353,7 +2373,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Netflix</t>
@@ -2387,17 +2411,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2450,7 +2474,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>ab15c844ecc542179e5afbaa8fc3454f</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>6cb80e58b933ec256b215690</t>
@@ -2477,7 +2505,7 @@
       <c r="AN10" s="3" t="inlineStr"/>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr"/>
@@ -2519,10 +2547,22 @@
       </c>
       <c r="BG10" s="3" t="inlineStr"/>
       <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2949,13 +2989,17 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3008,7 +3052,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>4f7764be2773431bad44bd2581fd591b</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>36d7ad0282838aa544c72d9d</t>
@@ -3033,7 +3081,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -3079,182 +3131,206 @@
       <c r="BH13" s="3" t="inlineStr"/>
       <c r="BI13" s="3" t="inlineStr"/>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Lumentum</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T20:27:58+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>美股盤前要點｜馬斯克、黃仁勛獲頒國家科學獎，蘋果被曝砍單iPhone 18 Pro系列</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>重大客戶流失</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/p/6916154</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>砍單</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>4e4f8c14a66f425a9dc585e7d10af8ed</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>e57f1cfc4516e759461039be</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>3671c2ebe9ded299a83099f5</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>LITE-MAJOR_CUSTOMER_LOSS-001</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/p/6916154</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_CUSTOMER_LOSS</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>砍單</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>e57f1cfc4516e759461039be</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>3671c2ebe9ded299a83099f5</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr">
-        <is>
-          <t>LITE-MAJOR_CUSTOMER_LOSS-001</t>
-        </is>
-      </c>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr">
         <is>
           <t>LITE</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr"/>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr"/>
+      <c r="BF14" s="2" t="inlineStr"/>
+      <c r="BG14" s="2" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3267,7 +3343,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Netflix</t>
@@ -3301,17 +3381,17 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3364,7 +3444,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>957f0b1511c0440c8ddb4795306a5b4a</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>c4cced58b22c5942630f7694</t>
@@ -3391,7 +3475,7 @@
       <c r="AN15" s="3" t="inlineStr"/>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr"/>
@@ -3433,10 +3517,22 @@
       </c>
       <c r="BG15" s="3" t="inlineStr"/>
       <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -4219,13 +4315,17 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4278,7 +4378,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>f8c3dcbb469a4f989f1db9349d9c98de</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>54976da73037e7e74d4da018</t>
@@ -4303,7 +4407,11 @@
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr"/>
       <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="3" t="inlineStr"/>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
@@ -4341,8 +4449,16 @@
       <c r="BH20" s="3" t="inlineStr"/>
       <c r="BI20" s="3" t="inlineStr"/>
       <c r="BJ20" s="3" t="inlineStr"/>
-      <c r="BK20" s="3" t="inlineStr"/>
-      <c r="BL20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4393,13 +4509,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4452,7 +4572,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>7a185d8eb0684f84ad7cc512aca1d2c0</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>a2047f7e5f8d52985250fd13</t>
@@ -4477,7 +4601,11 @@
       <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="inlineStr"/>
       <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="3" t="inlineStr"/>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
@@ -4523,8 +4651,16 @@
       <c r="BH21" s="3" t="inlineStr"/>
       <c r="BI21" s="3" t="inlineStr"/>
       <c r="BJ21" s="3" t="inlineStr"/>
-      <c r="BK21" s="3" t="inlineStr"/>
-      <c r="BL21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4777,13 +4913,17 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -4836,7 +4976,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>85cdb340e1f84350bfb3788ce61c9e9b</t>
+        </is>
+      </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
           <t>3304f9e80330a967e3017e37</t>
@@ -4861,7 +5005,11 @@
       <c r="AL23" s="3" t="inlineStr"/>
       <c r="AM23" s="3" t="inlineStr"/>
       <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="3" t="inlineStr"/>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
@@ -4907,8 +5055,16 @@
       <c r="BH23" s="3" t="inlineStr"/>
       <c r="BI23" s="3" t="inlineStr"/>
       <c r="BJ23" s="3" t="inlineStr"/>
-      <c r="BK23" s="3" t="inlineStr"/>
-      <c r="BL23" s="3" t="inlineStr"/>
+      <c r="BK23" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -6600,7 +6756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL14"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7040,13 +7196,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -7099,7 +7259,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>e64c9d39827d46e887fe11552793cc84</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>2026338b805069c2e1313420</t>
@@ -7124,7 +7288,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -7170,8 +7338,16 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -7184,7 +7360,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Netflix</t>
@@ -7218,17 +7398,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -7281,7 +7461,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>ab15c844ecc542179e5afbaa8fc3454f</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>6cb80e58b933ec256b215690</t>
@@ -7308,7 +7492,7 @@
       <c r="AN3" s="3" t="inlineStr"/>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr"/>
@@ -7350,10 +7534,22 @@
       </c>
       <c r="BG3" s="3" t="inlineStr"/>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7598,13 +7794,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -7657,7 +7857,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>4f7764be2773431bad44bd2581fd591b</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>36d7ad0282838aa544c72d9d</t>
@@ -7682,7 +7886,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -7728,8 +7936,16 @@
       <c r="BH5" s="3" t="inlineStr"/>
       <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -7742,20 +7958,24 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09T20:27:58+08:00</t>
+          <t>2026-10-09T20:17:58+08:00</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>美股盤前要點｜馬斯克、黃仁勛獲頒國家科學獎，蘋果被曝砍單iPhone 18 Pro系列</t>
+          <t>據《Puck News》報導，奈飛計劃裁員5%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -7766,7 +7986,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>重大客戶流失</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -7776,17 +7996,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -7796,7 +8016,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
@@ -7810,7 +8030,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/p/6916154</t>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-NFLX/news/</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -7826,12 +8046,12 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_CUSTOMER_LOSS</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>砍單</t>
+          <t>裁員</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -7839,20 +8059,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>957f0b1511c0440c8ddb4795306a5b4a</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>e57f1cfc4516e759461039be</t>
+          <t>c4cced58b22c5942630f7694</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>3671c2ebe9ded299a83099f5</t>
+          <t>b78c11d1ec8e3b594182e31d</t>
         </is>
       </c>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>LITE-MAJOR_CUSTOMER_LOSS-001</t>
+          <t>NFLX-WORKFORCE_REDUCTION-001</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr"/>
@@ -7866,7 +8090,7 @@
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -7883,7 +8107,7 @@
       <c r="BA6" s="3" t="inlineStr"/>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="BC6" s="3" t="inlineStr">
@@ -7893,391 +8117,423 @@
       </c>
       <c r="BD6" s="3" t="inlineStr">
         <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr"/>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Netflix</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:17:58+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>據《Puck News》報導，奈飛計劃裁員5%</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T19:00:52+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Market Chatter: ExxonMobil Blocks Settlement Over $5.2 Billion Kazakhstan Fine</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.94</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPR011SnBsQVFuS3E5NmdESGd1ZEs2SFJDdDBHRUdPY0Rxdm9iNXhSTXRnUWZPZXpjZjVYaWRLbnJMcjcyN2ZpNzZQQTZqZl9IZXp5Yl9GS0FoTDNZbjdneXNEVmN3VnRKYXNNMHcwR3NyMmpSWXhtcjVVWDVQSmpTb1lIVUNQb2lERG9jOHpWcnBrQ3g1V3MzSDFyNWRMQ2hDbWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>6971d1796b2f469da3f1a2b03c35d435</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>9b9875aaa852733b3ff4ea27</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>9fdae8b7f4a952806c55de98</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>XOM-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-NFLX/news/</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>c4cced58b22c5942630f7694</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>b78c11d1ec8e3b594182e31d</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr"/>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T19:00:52+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Market Chatter: ExxonMobil Blocks Settlement Over $5.2 Billion Kazakhstan Fine</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09T16:33:51+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Flydubai and Boeing: Targets of Everest Ransomware Campaign</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>資安攻擊</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>'-0.94</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>'-0.016</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPR011SnBsQVFuS3E5NmdESGd1ZEs2SFJDdDBHRUdPY0Rxdm9iNXhSTXRnUWZPZXpjZjVYaWRLbnJMcjcyN2ZpNzZQQTZqZl9IZXp5Yl9GS0FoTDNZbjdneXNEVmN3VnRKYXNNMHcwR3NyMmpSWXhtcjVVWDVQSmpTb1lIVUNQb2lERG9jOHpWcnBrQ3g1V3MzSDFyNWRMQ2hDbWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9IeWE5RWdISlZodEhwbG8yZTlvQnBLWGxKWVd5SHZWM0dnUE0tRFkyTlFRd3lCdmtBY09La2kzbVg1WkNjUmp0VFFIa2VsaGJkTmFFRDBpM24zVFI4b0diTTR4eXRXYW40V2ZyZFRXdjlsZGF4?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Cyber Magazine</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>CYBER_ATTACK</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>ransomware</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr">
-        <is>
-          <t>6971d1796b2f469da3f1a2b03c35d435</t>
-        </is>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>9b9875aaa852733b3ff4ea27</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>9fdae8b7f4a952806c55de98</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr">
-        <is>
-          <t>XOM-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>f8c3dcbb469a4f989f1db9349d9c98de</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>54976da73037e7e74d4da018</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>07b4a0c0b95defc58dd555c3</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>BA-CYBER_ATTACK-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF8" s="4" t="inlineStr"/>
-      <c r="BG8" s="4" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr">
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
@@ -8294,22 +8550,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09T16:33:51+08:00</t>
+          <t>2026-10-09T16:03:10+08:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Flydubai and Boeing: Targets of Everest Ransomware Campaign</t>
+          <t>PEP Q3 Deep Dive: International Growth Offsets North American Beverage Weakness, Margin Pressures Persist</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -8320,7 +8576,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>資安攻擊</t>
+          <t>營運惡化</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -8330,13 +8586,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -8346,7 +8606,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>'-0.016</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
@@ -8360,28 +8620,28 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9IeWE5RWdISlZodEhwbG8yZTlvQnBLWGxKWVd5SHZWM0dnUE0tRFkyTlFRd3lCdmtBY09La2kzbVg1WkNjUmp0VFFIa2VsaGJkTmFFRDBpM24zVFI4b0diTTR4eXRXYW40V2ZyZFRXdjlsZGF4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYnQ5Ykt5akdWZUw4UU1kNTBJdEZsbk1mcl9hTGxGZDlUeVFfRDlCRVgxWXpwLVBKUlhUY2pjM0FWcGg2UzRFaUFNQXRuQ0xMMDRGUG1iLVNLaGN5Vlh6a05WZndUSkc1ajJjaHl0SlJ6NHlRbTZSZmZwNmFYWUxfbVBRQ2VBcU9rZVhsdFVHc3NWcjFyUkZOUkJDTQ?oc=5</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Cyber Magazine</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>CYBER_ATTACK</t>
+          <t>OPERATING_DETERIORATION</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>ransomware</t>
+          <t>margin pressure</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -8389,20 +8649,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>7a185d8eb0684f84ad7cc512aca1d2c0</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>54976da73037e7e74d4da018</t>
+          <t>a2047f7e5f8d52985250fd13</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>07b4a0c0b95defc58dd555c3</t>
+          <t>75fdb756567aabe6eaf2652d</t>
         </is>
       </c>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>BA-CYBER_ATTACK-001</t>
+          <t>PEP-OPERATING_DETERIORATION-001</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr"/>
@@ -8414,7 +8678,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -8422,14 +8690,18 @@
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="inlineStr"/>
       <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX9" s="3" t="inlineStr"/>
       <c r="AY9" s="3" t="inlineStr"/>
       <c r="AZ9" s="3" t="inlineStr"/>
       <c r="BA9" s="3" t="inlineStr"/>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="BC9" s="3" t="inlineStr">
@@ -8440,586 +8712,622 @@
       <c r="BD9" s="3" t="inlineStr"/>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG9" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
       <c r="BI9" s="3" t="inlineStr"/>
       <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>PepsiCo, Inc.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T16:03:10+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>PEP Q3 Deep Dive: International Growth Offsets North American Beverage Weakness, Margin Pressures Persist</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T15:31:30+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Corteva agrees to end pesticide loyalty programmes in proposed settlement with Federal Trade Commission</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>0.126</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNTUIxVF9TUl81LXpaVHhkbER0Q0FmUlR4UjVBd3NJbTZINTZiUHdFOUhmd082RDV2TW5ESS05a0FFd2pjbks4c05EQzNQaUlwZVRRUTNvWVJPb0JEV0lKaHprQ04zSFB1LXdGOVRFUTI2RWs2N3ZpcnZyczQ0UWdGcEtnSGRXZFlhZ2YtQXhvUktvU28yYnRQOTVnZFhZa1BTZTR3SUxacmRHbldTTG9NT3hkY2FTeVJnMExnTUFGUWFSVFVKdkZRZ0hrV3MtZUY4SVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>Oils &amp; Fats International</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>ce83585cd2a24cb6a6f71f0edf84f270</t>
+        </is>
+      </c>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>df60c898bd5a51b7ca55e7f0</t>
+        </is>
+      </c>
+      <c r="AD10" s="4" t="inlineStr">
+        <is>
+          <t>51d2fa07a12405a6d72f546a</t>
+        </is>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>CTVA-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF10" s="4" t="inlineStr"/>
+      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
+      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>0.853</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQYnQ5Ykt5akdWZUw4UU1kNTBJdEZsbk1mcl9hTGxGZDlUeVFfRDlCRVgxWXpwLVBKUlhUY2pjM0FWcGg2UzRFaUFNQXRuQ0xMMDRGUG1iLVNLaGN5Vlh6a05WZndUSkc1ajJjaHl0SlJ6NHlRbTZSZmZwNmFYWUxfbVBRQ2VBcU9rZVhsdFVHc3NWcjFyUkZOUkJDTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>a2047f7e5f8d52985250fd13</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>75fdb756567aabe6eaf2652d</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr">
-        <is>
-          <t>PEP-OPERATING_DETERIORATION-001</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="AP10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AR10" s="4" t="inlineStr"/>
+      <c r="AS10" s="4" t="inlineStr"/>
+      <c r="AT10" s="4" t="inlineStr"/>
+      <c r="AU10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AW10" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX10" s="4" t="inlineStr"/>
+      <c r="AY10" s="4" t="inlineStr"/>
+      <c r="AZ10" s="4" t="inlineStr"/>
+      <c r="BA10" s="4" t="inlineStr"/>
+      <c r="BB10" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC10" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BD10" s="4" t="inlineStr"/>
+      <c r="BE10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG10" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T15:31:30+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Corteva agrees to end pesticide loyalty programmes in proposed settlement with Federal Trade Commission</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:15:46+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Netflix Is Sharpening the Layoff Axe</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>0.126</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>'-0.918</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNTUIxVF9TUl81LXpaVHhkbER0Q0FmUlR4UjVBd3NJbTZINTZiUHdFOUhmd082RDV2TW5ESS05a0FFd2pjbks4c05EQzNQaUlwZVRRUTNvWVJPb0JEV0lKaHprQ04zSFB1LXdGOVRFUTI2RWs2N3ZpcnZyczQ0UWdGcEtnSGRXZFlhZ2YtQXhvUktvU28yYnRQOTVnZFhZa1BTZTR3SUxacmRHbldTTG9NT3hkY2FTeVJnMExnTUFGUWFSVFVKdkZRZ0hrV3MtZUY4SVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>Oils &amp; Fats International</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE90dm1nWTNuR1dCeVJkcXp1SVBvMlpMTVQwUmJ3US1UYTBwbjY1b1piazlVRE8yVWZsQ29xOW85Yk5nbXlJWVU5RFhjTDhyZDBjSndja1g5bUx6cXgtVVNsdzlsRnJTZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Puck</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>ce83585cd2a24cb6a6f71f0edf84f270</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>df60c898bd5a51b7ca55e7f0</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>51d2fa07a12405a6d72f546a</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr">
-        <is>
-          <t>CTVA-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>85cdb340e1f84350bfb3788ce61c9e9b</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>3304f9e80330a967e3017e37</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>d1e2fb9f6d8799eaf17d49d8</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>NFLX-WORKFORCE_REDUCTION-001</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BC11" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="4" t="inlineStr">
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr">
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T14:15:46+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Netflix Is Sharpening the Layoff Axe</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T05:31:41+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>美國運通因反洗錢計劃不完善被罰款3.5億美元</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NYSE-AXP/news/</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>罰款</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>771d5e73b83e44c9a35cfc84062deb2c</t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>08957e2647ed4bc7fc7d5b67</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>ba7c5621b413520ed3012946</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>AXP-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>'-0.918</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE90dm1nWTNuR1dCeVJkcXp1SVBvMlpMTVQwUmJ3US1UYTBwbjY1b1piazlVRE8yVWZsQ29xOW85Yk5nbXlJWVU5RFhjTDhyZDBjSndja1g5bUx6cXgtVVNsdzlsRnJTZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>Puck</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>3304f9e80330a967e3017e37</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>d1e2fb9f6d8799eaf17d49d8</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr">
-        <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr"/>
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="BC12" s="4" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="BE12" s="4" t="inlineStr"/>
+      <c r="BF12" s="4" t="inlineStr"/>
+      <c r="BG12" s="4" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -9032,20 +9340,24 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>SYY</t>
+        </is>
+      </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sysco Corporation Common Stock</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T05:31:41+08:00</t>
+          <t>2026-10-09T01:06:24+08:00</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>美國運通因反洗錢計劃不完善被罰款3.5億美元</t>
+          <t>Sysco-Restaurant Depot Deal Still Awaits FTC Review Six Months After Announcement</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -9056,7 +9368,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -9086,7 +9398,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>'-0.035</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -9095,17 +9407,17 @@
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-AXP/news/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTDY2cGxiOTFDVUpSZVdKNUFYUWdDa3ZKTndkQ3JFaUxYd2ZMb2pUcnVJM2J3emxuTE1wMHNKdndvRlFDTEtKWXNpbGs3Yk9BWVVkdDJWLVk5dHBhbTBBWER6UFdkY3RHWnd6MmtOZUcyYUdnVDN4UGNXWnpPQnNOVVR4ZVNqX3lsdDJuZ2FPZkhXLXQ3dHNQekFDYWkyOTdETWNFX1VTSUd2ZWxfdmJWbXd6azAzX0drY2pOMVdvZlQ?oc=5</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Distribution Strategy Group</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr"/>
@@ -9116,12 +9428,12 @@
       </c>
       <c r="Y13" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z13" s="4" t="inlineStr">
         <is>
-          <t>罰款</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA13" s="4" t="inlineStr">
@@ -9131,22 +9443,22 @@
       </c>
       <c r="AB13" s="4" t="inlineStr">
         <is>
-          <t>771d5e73b83e44c9a35cfc84062deb2c</t>
+          <t>914055f1ae794100999137c39b79a1bc</t>
         </is>
       </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>08957e2647ed4bc7fc7d5b67</t>
+          <t>e72a515e26befc5ce8f1598e</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>ba7c5621b413520ed3012946</t>
+          <t>08f126b0d1618ed5c5092d09</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
         <is>
-          <t>AXP-REGULATORY_PENALTY-001</t>
+          <t>SYY-REGULATORY_INVESTIGATION-001</t>
         </is>
       </c>
       <c r="AF13" s="4" t="inlineStr"/>
@@ -9170,29 +9482,41 @@
       <c r="AT13" s="4" t="inlineStr"/>
       <c r="AU13" s="4" t="inlineStr"/>
       <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
+      <c r="AW13" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX13" s="4" t="inlineStr"/>
       <c r="AY13" s="4" t="inlineStr"/>
       <c r="AZ13" s="4" t="inlineStr"/>
       <c r="BA13" s="4" t="inlineStr"/>
       <c r="BB13" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr">
-        <is>
-          <t>AXP</t>
-        </is>
-      </c>
-      <c r="BE13" s="4" t="inlineStr"/>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr"/>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD13" s="4" t="inlineStr"/>
+      <c r="BE13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG13" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
       <c r="BH13" s="4" t="inlineStr"/>
       <c r="BI13" s="4" t="inlineStr"/>
       <c r="BJ13" s="4" t="inlineStr"/>
@@ -9203,214 +9527,12 @@
       </c>
       <c r="BL13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T15:43:17.016263+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>SYY</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Sysco Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09T01:06:24+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Sysco-Restaurant Depot Deal Still Awaits FTC Review Six Months After Announcement</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>'-0.035</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTDY2cGxiOTFDVUpSZVdKNUFYUWdDa3ZKTndkQ3JFaUxYd2ZMb2pUcnVJM2J3emxuTE1wMHNKdndvRlFDTEtKWXNpbGs3Yk9BWVVkdDJWLVk5dHBhbTBBWER6UFdkY3RHWnd6MmtOZUcyYUdnVDN4UGNXWnpPQnNOVVR4ZVNqX3lsdDJuZ2FPZkhXLXQ3dHNQekFDYWkyOTdETWNFX1VTSUd2ZWxfdmJWbXd6azAzX0drY2pOMVdvZlQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>Distribution Strategy Group</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>914055f1ae794100999137c39b79a1bc</t>
-        </is>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>e72a515e26befc5ce8f1598e</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>08f126b0d1618ed5c5092d09</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>SYY-REGULATORY_INVESTIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>SYY</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG14" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL14" s="4" t="inlineStr">
-        <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL14"/>
+  <autoFilter ref="A1:BL13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9421,7 +9543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL4"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9812,546 +9934,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Netflix</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T21:06:54+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>奈飛據報計劃裁員約5%</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2703699</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>6cb80e58b933ec256b215690</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>a8be937b4df9356931725bf5</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr">
-        <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Lumentum</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:27:58+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>美股盤前要點｜馬斯克、黃仁勛獲頒國家科學獎，蘋果被曝砍單iPhone 18 Pro系列</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>重大客戶流失</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/p/6916154</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_CUSTOMER_LOSS</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>砍單</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>e57f1cfc4516e759461039be</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>3671c2ebe9ded299a83099f5</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>LITE-MAJOR_CUSTOMER_LOSS-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr"/>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Netflix</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09T20:17:58+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>據《Puck News》報導，奈飛計劃裁員5%</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-NFLX/news/</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>c4cced58b22c5942630f7694</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>b78c11d1ec8e3b594182e31d</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>NFLX-WORKFORCE_REDUCTION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr"/>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr"/>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL4"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-09.xlsx
+++ b/news_daily/2026-10-09.xlsx
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>a5bde92e4e1342b68e07bcdc7b7e02ab</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>f703a227309edea3ee0776c8</t>
@@ -987,7 +995,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1033,8 +1045,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1272,28 +1292,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1333,7 +1357,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1346,7 +1370,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>42a8f265ee1641f2b42b18b18b693eaf</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>52df1f102fed0f29212eb803</t>
@@ -1371,7 +1399,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1415,10 +1447,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1454,28 +1498,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1515,7 +1563,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1528,7 +1576,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>784c80be0f52454c873a3948ce729e17</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>2969ada0f0a1833df5374d13</t>
@@ -1553,7 +1605,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1597,10 +1653,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1834,28 +1902,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1895,7 +1967,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1908,7 +1980,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>3409c2b357e54b11a3c941538a717167</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>9270cead2be06be3d36bd556</t>
@@ -1933,7 +2009,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1969,10 +2049,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2023,13 +2115,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2082,7 +2178,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>1012d41d5b4f44d5b50246cec3023abe</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>0b439f5e5cb418227093e3d3</t>
@@ -2107,7 +2207,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2153,8 +2257,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2792,28 +2904,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2853,7 +2969,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2866,7 +2982,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>c34a3516ba0f49299277b38f318cd7a2</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>9967239d95bbcf5983a68996</t>
@@ -2891,7 +3011,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2935,10 +3059,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3777,13 +3913,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3836,7 +3976,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>2110a99593354dbebc36e59181d66b0e</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>c571fbf60b3f0a1336ff9bd6</t>
@@ -3861,7 +4005,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3899,8 +4047,16 @@
       <c r="BH17" s="2" t="inlineStr"/>
       <c r="BI17" s="2" t="inlineStr"/>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3936,28 +4092,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3997,7 +4157,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -4010,7 +4170,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>994166926ee746b1bad58a7973c3733d</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>7e3dd57a4c5988099e3b8774</t>
@@ -4035,7 +4199,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4079,10 +4247,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4133,13 +4313,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4192,7 +4376,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>ee90d4deaa714542a786b901066e7f66</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>a99c5386bc347875bbbec164</t>
@@ -4217,7 +4405,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4263,8 +4455,16 @@
       <c r="BH19" s="2" t="inlineStr"/>
       <c r="BI19" s="2" t="inlineStr"/>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -5286,28 +5486,32 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5347,7 +5551,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5360,7 +5564,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>9611d47609504e31a5976a8d7ced79f8</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>5d199898ddcb9637b5f64421</t>
@@ -5385,7 +5593,11 @@
       <c r="AL25" s="2" t="inlineStr"/>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="2" t="inlineStr"/>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="inlineStr"/>
@@ -5429,10 +5641,22 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5468,28 +5692,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5529,7 +5757,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5542,7 +5770,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>bba9a97efcfa4b34bfa0c8ff4d8a6366</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>dfdbcd3d97525867c3020598</t>
@@ -5567,7 +5799,11 @@
       <c r="AL26" s="2" t="inlineStr"/>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr"/>
-      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr"/>
@@ -5611,10 +5847,22 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5665,13 +5913,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5724,7 +5976,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>c6c58bd457924ba4a139b2f6a7bf7c1d</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>21b04978ddaf12dc65c5297a</t>
@@ -5749,7 +6005,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5787,8 +6047,16 @@
       <c r="BH27" s="2" t="inlineStr"/>
       <c r="BI27" s="2" t="inlineStr"/>
       <c r="BJ27" s="2" t="inlineStr"/>
-      <c r="BK27" s="2" t="inlineStr"/>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6045,13 +6313,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6104,7 +6376,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>f6c3909783934f0b8a99f7034f9021c4</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>ca70bc4997a92082152f8dfa</t>
@@ -6129,7 +6405,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -6167,8 +6447,16 @@
       <c r="BH29" s="2" t="inlineStr"/>
       <c r="BI29" s="2" t="inlineStr"/>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -6406,28 +6694,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6467,7 +6759,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6480,7 +6772,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>9e44f423c2b14e80937019e7fccfa6a0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>0788b31f1fcf4575cd92dcf0</t>
@@ -6505,7 +6801,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6549,10 +6849,22 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">

--- a/news_daily/2026-10-09.xlsx
+++ b/news_daily/2026-10-09.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$32</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,21 +71,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5277,7 +5266,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>American Express</t>
@@ -5439,7 +5432,11 @@
       <c r="BF24" s="4" t="inlineStr"/>
       <c r="BG24" s="4" t="inlineStr"/>
       <c r="BH24" s="4" t="inlineStr"/>
-      <c r="BI24" s="4" t="inlineStr"/>
+      <c r="BI24" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ24" s="4" t="inlineStr"/>
       <c r="BK24" s="4" t="inlineStr">
         <is>
@@ -9466,7 +9463,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
           <t>American Express</t>
@@ -9628,7 +9629,11 @@
       <c r="BF12" s="4" t="inlineStr"/>
       <c r="BG12" s="4" t="inlineStr"/>
       <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ12" s="4" t="inlineStr"/>
       <c r="BK12" s="4" t="inlineStr">
         <is>
